--- a/verificables revisión sistemática/S5_listado_184_estudios.xlsx
+++ b/verificables revisión sistemática/S5_listado_184_estudios.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-26</t>
+          <t>Generado el 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">

--- a/verificables revisión sistemática/S5_listado_184_estudios.xlsx
+++ b/verificables revisión sistemática/S5_listado_184_estudios.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-28</t>
+          <t>Generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S5_listado_184_estudios.xlsx
+++ b/verificables revisión sistemática/S5_listado_184_estudios.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-31</t>
+          <t>Generado el 2026-09-01</t>
         </is>
       </c>
     </row>
